--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128702169</v>
+        <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>91746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790482</v>
+        <v>790462</v>
       </c>
       <c r="R4" t="n">
-        <v>7366613</v>
+        <v>7366638</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128702162</v>
+        <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>91746</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>790462</v>
+        <v>790482</v>
       </c>
       <c r="R5" t="n">
-        <v>7366638</v>
+        <v>7366613</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91746</v>
+        <v>91748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91748</v>
+        <v>91749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91749</v>
+        <v>91776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91776</v>
+        <v>91781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91781</v>
+        <v>91786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91786</v>
+        <v>91790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91802</v>
+        <v>91805</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128702174</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128702173</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128702162</v>
       </c>
       <c r="B4" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28718-2025 artfynd.xlsx
+++ b/artfynd/A 28718-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128702169</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
